--- a/sheet/AmmoCardData.xlsx
+++ b/sheet/AmmoCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881B30E1-611E-4A03-8B44-D87988DD8700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A949567B-2CAA-4719-949E-3AA489D87DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>石子</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -100,6 +100,14 @@
   </si>
   <si>
     <t>改变同房间中1张其他怪物牌的阵营。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>传送吹箭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将同房间1张其他怪物牌移动到楼层区另一个房间。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -428,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -538,6 +546,20 @@
         <v>13</v>
       </c>
     </row>
+    <row r="8" spans="1:7" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
